--- a/faker/suppliers.xlsx
+++ b/faker/suppliers.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>45752.08668981482</v>
+        <v>45752.63733796297</v>
       </c>
     </row>
     <row r="3">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>44694.33569444445</v>
+        <v>44694.8863425926</v>
       </c>
     </row>
     <row r="4">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>44823.40149305556</v>
+        <v>44823.95214120371</v>
       </c>
     </row>
     <row r="5">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>44499.79076388889</v>
+        <v>44500.34141203704</v>
       </c>
     </row>
     <row r="6">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>44810.63940972222</v>
+        <v>44811.19005787037</v>
       </c>
     </row>
     <row r="7">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>45419.12621527778</v>
+        <v>45419.67686342593</v>
       </c>
     </row>
     <row r="8">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>44650.72149305556</v>
+        <v>44651.27214120371</v>
       </c>
     </row>
     <row r="9">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>45094.4687037037</v>
+        <v>45095.01935185185</v>
       </c>
     </row>
     <row r="10">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>44228.06086805555</v>
+        <v>44228.6115162037</v>
       </c>
     </row>
     <row r="11">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2023-05-26 02:59:55</t>
+          <t>2023-05-26 16:12:51</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>44584.91371527778</v>
+        <v>44585.46436342593</v>
       </c>
     </row>
     <row r="13">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>44936.33621527778</v>
+        <v>44936.88686342593</v>
       </c>
     </row>
     <row r="14">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>44666.6215625</v>
+        <v>44667.17221064815</v>
       </c>
     </row>
     <row r="15">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>44922.72665509259</v>
+        <v>44923.27730324074</v>
       </c>
     </row>
     <row r="16">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>44378.21517361111</v>
+        <v>44378.76582175926</v>
       </c>
     </row>
     <row r="17">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>44828.62168981481</v>
+        <v>44829.17233796296</v>
       </c>
     </row>
     <row r="18">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>44390.05849537037</v>
+        <v>44390.60914351852</v>
       </c>
     </row>
     <row r="19">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>45065.9425462963</v>
+        <v>45066.49319444445</v>
       </c>
     </row>
     <row r="20">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>45260.98553240741</v>
+        <v>45261.53618055556</v>
       </c>
     </row>
     <row r="21">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>44999.31388888889</v>
+        <v>44999.86453703704</v>
       </c>
     </row>
     <row r="22">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>44964.7315625</v>
+        <v>44965.28221064815</v>
       </c>
     </row>
     <row r="23">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>44271.30645833333</v>
+        <v>44271.85710648148</v>
       </c>
     </row>
     <row r="24">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>45157.59211805555</v>
+        <v>45158.1427662037</v>
       </c>
     </row>
     <row r="25">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2021-05-15 21:09:38</t>
+          <t>2021-05-16 10:22:34</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>44510.20237268518</v>
+        <v>44510.75302083333</v>
       </c>
     </row>
     <row r="27">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>44896.32261574074</v>
+        <v>44896.87326388889</v>
       </c>
     </row>
     <row r="28">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>44873.5371875</v>
+        <v>44874.08783564815</v>
       </c>
     </row>
     <row r="29">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2024-11-16 20:33:00</t>
+          <t>2024-11-17 09:45:56</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>44220.81672453704</v>
+        <v>44221.36737268518</v>
       </c>
     </row>
     <row r="31">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>45068.42428240741</v>
+        <v>45068.97493055555</v>
       </c>
     </row>
     <row r="32">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>44752.69188657407</v>
+        <v>44753.24253472222</v>
       </c>
     </row>
     <row r="33">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>45135.54991898148</v>
+        <v>45136.10056712963</v>
       </c>
     </row>
     <row r="34">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>44684.93347222222</v>
+        <v>44685.48412037037</v>
       </c>
     </row>
     <row r="35">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>44557.12574074074</v>
+        <v>44557.67638888889</v>
       </c>
     </row>
     <row r="36">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>44562.19636574074</v>
+        <v>44562.74701388889</v>
       </c>
     </row>
     <row r="37">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44712.72001157407</v>
+        <v>44713.27065972222</v>
       </c>
     </row>
     <row r="38">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>44847.43388888889</v>
+        <v>44847.98453703704</v>
       </c>
     </row>
     <row r="39">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>44699.06976851852</v>
+        <v>44699.62041666666</v>
       </c>
     </row>
     <row r="40">
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>44986.4421875</v>
+        <v>44986.99283564815</v>
       </c>
     </row>
     <row r="41">
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>45533.19476851852</v>
+        <v>45533.74541666666</v>
       </c>
     </row>
     <row r="42">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>45333.78534722222</v>
+        <v>45334.33599537037</v>
       </c>
     </row>
     <row r="43">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>44666.6215625</v>
+        <v>44667.17221064815</v>
       </c>
     </row>
     <row r="44">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>44765.31873842593</v>
+        <v>44765.86938657407</v>
       </c>
     </row>
     <row r="45">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>44315.25291666666</v>
+        <v>44315.80356481481</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>44507.07848379629</v>
+        <v>44507.62913194444</v>
       </c>
     </row>
     <row r="47">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>44956.57300925926</v>
+        <v>44957.12365740741</v>
       </c>
     </row>
     <row r="48">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>44571.63535879629</v>
+        <v>44572.18600694444</v>
       </c>
     </row>
     <row r="49">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>44587.63739583334</v>
+        <v>44588.18804398148</v>
       </c>
     </row>
     <row r="50">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>44461.48307870371</v>
+        <v>44462.03372685185</v>
       </c>
     </row>
     <row r="51">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>44850.76649305555</v>
+        <v>44851.3171412037</v>
       </c>
     </row>
     <row r="52">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>44698.91108796297</v>
+        <v>44699.46173611111</v>
       </c>
     </row>
   </sheetData>

--- a/faker/suppliers.xlsx
+++ b/faker/suppliers.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>45752.63733796297</v>
+        <v>45753.06971064815</v>
       </c>
     </row>
     <row r="3">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>44694.8863425926</v>
+        <v>44695.31871527778</v>
       </c>
     </row>
     <row r="4">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>44823.95214120371</v>
+        <v>44824.38451388889</v>
       </c>
     </row>
     <row r="5">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>44500.34141203704</v>
+        <v>44500.77378472222</v>
       </c>
     </row>
     <row r="6">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>44811.19005787037</v>
+        <v>44811.62243055556</v>
       </c>
     </row>
     <row r="7">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>45419.67686342593</v>
+        <v>45420.10923611111</v>
       </c>
     </row>
     <row r="8">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>44651.27214120371</v>
+        <v>44651.70451388889</v>
       </c>
     </row>
     <row r="9">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>45095.01935185185</v>
+        <v>45095.45172453704</v>
       </c>
     </row>
     <row r="10">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>44228.6115162037</v>
+        <v>44229.04388888889</v>
       </c>
     </row>
     <row r="11">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2023-05-26 16:12:51</t>
+          <t>2023-05-27 02:35:28</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>44585.46436342593</v>
+        <v>44585.89673611111</v>
       </c>
     </row>
     <row r="13">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>44936.88686342593</v>
+        <v>44937.31923611111</v>
       </c>
     </row>
     <row r="14">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>44667.17221064815</v>
+        <v>44667.60458333333</v>
       </c>
     </row>
     <row r="15">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>44923.27730324074</v>
+        <v>44923.70967592593</v>
       </c>
     </row>
     <row r="16">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>44378.76582175926</v>
+        <v>44379.19819444444</v>
       </c>
     </row>
     <row r="17">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>44829.17233796296</v>
+        <v>44829.60471064815</v>
       </c>
     </row>
     <row r="18">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>44390.60914351852</v>
+        <v>44391.0415162037</v>
       </c>
     </row>
     <row r="19">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>45066.49319444445</v>
+        <v>45066.92556712963</v>
       </c>
     </row>
     <row r="20">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>45261.53618055556</v>
+        <v>45261.96855324074</v>
       </c>
     </row>
     <row r="21">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>44999.86453703704</v>
+        <v>45000.29690972222</v>
       </c>
     </row>
     <row r="22">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>44965.28221064815</v>
+        <v>44965.71458333333</v>
       </c>
     </row>
     <row r="23">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>44271.85710648148</v>
+        <v>44272.28947916667</v>
       </c>
     </row>
     <row r="24">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>45158.1427662037</v>
+        <v>45158.57513888889</v>
       </c>
     </row>
     <row r="25">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2021-05-16 10:22:34</t>
+          <t>2021-05-16 20:45:11</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>44510.75302083333</v>
+        <v>44511.18539351852</v>
       </c>
     </row>
     <row r="27">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>44896.87326388889</v>
+        <v>44897.30563657408</v>
       </c>
     </row>
     <row r="28">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>44874.08783564815</v>
+        <v>44874.52020833334</v>
       </c>
     </row>
     <row r="29">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2024-11-17 09:45:56</t>
+          <t>2024-11-17 20:08:33</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>44221.36737268518</v>
+        <v>44221.79974537037</v>
       </c>
     </row>
     <row r="31">
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>45068.97493055555</v>
+        <v>45069.40730324074</v>
       </c>
     </row>
     <row r="32">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>44753.24253472222</v>
+        <v>44753.67490740741</v>
       </c>
     </row>
     <row r="33">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>45136.10056712963</v>
+        <v>45136.53293981482</v>
       </c>
     </row>
     <row r="34">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>44685.48412037037</v>
+        <v>44685.91649305556</v>
       </c>
     </row>
     <row r="35">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>44557.67638888889</v>
+        <v>44558.10876157408</v>
       </c>
     </row>
     <row r="36">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>44562.74701388889</v>
+        <v>44563.17938657408</v>
       </c>
     </row>
     <row r="37">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44713.27065972222</v>
+        <v>44713.70303240741</v>
       </c>
     </row>
     <row r="38">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>44847.98453703704</v>
+        <v>44848.41690972223</v>
       </c>
     </row>
     <row r="39">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>44699.62041666666</v>
+        <v>44700.05278935185</v>
       </c>
     </row>
     <row r="40">
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>44986.99283564815</v>
+        <v>44987.42520833333</v>
       </c>
     </row>
     <row r="41">
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>45533.74541666666</v>
+        <v>45534.17778935185</v>
       </c>
     </row>
     <row r="42">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>45334.33599537037</v>
+        <v>45334.76836805556</v>
       </c>
     </row>
     <row r="43">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>44667.17221064815</v>
+        <v>44667.60458333333</v>
       </c>
     </row>
     <row r="44">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>44765.86938657407</v>
+        <v>44766.30175925926</v>
       </c>
     </row>
     <row r="45">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>44315.80356481481</v>
+        <v>44316.2359375</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>44507.62913194444</v>
+        <v>44508.06150462963</v>
       </c>
     </row>
     <row r="47">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>44957.12365740741</v>
+        <v>44957.55603009259</v>
       </c>
     </row>
     <row r="48">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>44572.18600694444</v>
+        <v>44572.61837962963</v>
       </c>
     </row>
     <row r="49">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>44588.18804398148</v>
+        <v>44588.62041666666</v>
       </c>
     </row>
     <row r="50">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>44462.03372685185</v>
+        <v>44462.46609953704</v>
       </c>
     </row>
     <row r="51">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>44851.3171412037</v>
+        <v>44851.74951388889</v>
       </c>
     </row>
     <row r="52">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>44699.46173611111</v>
+        <v>44699.8941087963</v>
       </c>
     </row>
   </sheetData>
